--- a/diseases/d035/2000-2004.xlsx
+++ b/diseases/d035/2000-2004.xlsx
@@ -4465,9 +4465,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -4761,9 +4758,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +5051,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5344,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -5649,9 +5637,6 @@
       <c r="O35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -5945,9 +5930,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6241,9 +6223,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6537,9 +6516,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -6833,9 +6809,6 @@
       <c r="O43" t="n">
         <v>16</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.03401109799133006</v>
       </c>
@@ -7129,9 +7102,6 @@
       <c r="O45" t="n">
         <v>27</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.05739372786036948</v>
       </c>
@@ -7425,9 +7395,6 @@
       <c r="O47" t="n">
         <v>72</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1530499409609853</v>
       </c>
@@ -7721,9 +7688,6 @@
       <c r="O49" t="n">
         <v>10</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.02125693624458129</v>
       </c>
@@ -8165,9 +8129,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -8609,9 +8570,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9011,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9452,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -9941,9 +9893,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -10385,9 +10334,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10775,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -11273,9 +11216,6 @@
       <c r="O73" t="n">
         <v>2</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -11717,9 +11657,6 @@
       <c r="O76" t="n">
         <v>16</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.03382726746473013</v>
       </c>
@@ -12161,9 +12098,6 @@
       <c r="O79" t="n">
         <v>56</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1183954361265555</v>
       </c>
@@ -12605,9 +12539,6 @@
       <c r="O82" t="n">
         <v>37</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.07822555601218843</v>
       </c>
@@ -13049,9 +12980,6 @@
       <c r="O85" t="n">
         <v>5</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -13493,9 +13421,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14085,9 +14010,6 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -14677,9 +14599,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15269,9 +15188,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -15713,9 +15629,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16305,9 +16218,6 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -16897,9 +16807,6 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -17489,9 +17396,6 @@
       <c r="O115" t="n">
         <v>5</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -18081,9 +17985,6 @@
       <c r="O119" t="n">
         <v>14</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.02946490025852398</v>
       </c>
@@ -18673,9 +18574,6 @@
       <c r="O123" t="n">
         <v>56</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.1178596010340959</v>
       </c>
@@ -19265,9 +19163,6 @@
       <c r="O127" t="n">
         <v>28</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.05892980051704796</v>
       </c>
@@ -19857,9 +19752,6 @@
       <c r="O131" t="n">
         <v>9</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -20449,9 +20341,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -21633,9 +21519,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22225,9 +22108,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -22817,9 +22697,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -23409,9 +23286,6 @@
       <c r="O155" t="n">
         <v>5</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -24001,9 +23875,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -24593,9 +24464,6 @@
       <c r="O163" t="n">
         <v>13</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.02725533979541367</v>
       </c>
@@ -25185,9 +25053,6 @@
       <c r="O167" t="n">
         <v>10</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.02096564599647205</v>
       </c>
@@ -25777,9 +25642,6 @@
       <c r="O171" t="n">
         <v>71</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1488560865749515</v>
       </c>
@@ -26369,9 +26231,6 @@
       <c r="O175" t="n">
         <v>32</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.06709006718871055</v>
       </c>
@@ -26960,9 +26819,6 @@
       </c>
       <c r="O179" t="n">
         <v>4</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0.008386258398588819</v>
